--- a/脚本/汇总脚本/DML/配置脚本管理/业务数据维护脚本/业务数据维护配置表TMP/CHB_INFOMGR_CONFIG(TMP).xlsx
+++ b/脚本/汇总脚本/DML/配置脚本管理/业务数据维护脚本/业务数据维护配置表TMP/CHB_INFOMGR_CONFIG(TMP).xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511" concurrentCalc="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="103">
   <si>
     <t>序号</t>
   </si>
@@ -1883,6 +1883,9 @@
       <c r="G41" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I41" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
@@ -1906,6 +1909,10 @@
       <c r="G42" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I42" s="1" t="str">
+        <f>CONCATENATE("insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (",B42,",'",C42,"','",D42,"','",E42,"','",F42,"','",G42,"','",H42,"');")</f>
+        <v>insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (f_guid(),'CHB_INTERF_ERRODATA','DATAUUID','uuid技术主键','U','N','');</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
@@ -1929,6 +1936,10 @@
       <c r="G43" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I43" s="1" t="str">
+        <f t="shared" ref="I43:I45" si="2">CONCATENATE("insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (",B43,",'",C43,"','",D43,"','",E43,"','",F43,"','",G43,"','",H43,"');")</f>
+        <v>insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (f_guid(),'CHB_INTERF_ERRODATA','FIRE_NAME','文件名称','T','N','');</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
@@ -1952,6 +1963,10 @@
       <c r="G44" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="I44" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (f_guid(),'CHB_INTERF_ERRODATA','DATAID','业务主键','T','Y','');</v>
+      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
@@ -1974,6 +1989,10 @@
       </c>
       <c r="G45" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="I45" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into CHB_INFOMGR_CONFIG (BASEINFORMATIONID,BASETABLEID,BASECOLUMNID,BASECOLUMNNAME,BASECOLUMNTYPE,BUSINESSPKFLAG,DICTCODE) values (f_guid(),'CHB_INTERF_ERRODATA','ERR_MSG','错误信息','T','N','');</v>
       </c>
     </row>
   </sheetData>
